--- a/Formato 3/BT-cantidades-Mompox.xlsx
+++ b/Formato 3/BT-cantidades-Mompox.xlsx
@@ -1760,149 +1760,63 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="37" fontId="5" fillId="0" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="56" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="61" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1910,32 +1824,181 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="55" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="37" fontId="5" fillId="0" borderId="63" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="51" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="52" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1944,71 +2007,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="0" borderId="67" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="57" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="64" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="68" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2424,7 +2424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AB55"/>
+  <dimension ref="A1:AB54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.7265625" customWidth="1" style="169" min="1" max="1"/>
@@ -5548,7 +5548,7 @@
     </row>
     <row r="46" ht="90.75" customHeight="1" s="169">
       <c r="A46" s="281" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B46" s="281" t="inlineStr">
         <is>
@@ -5561,27 +5561,27 @@
       </c>
       <c r="E46" s="281" t="inlineStr">
         <is>
-          <t>unidades</t>
+          <t>Unidades</t>
         </is>
       </c>
       <c r="F46" s="281" t="inlineStr">
         <is>
-          <t>PROELECTRA DE COLOMBIA S.A.S</t>
+          <t>COBRES DE COLOMBIA S.A.S.</t>
         </is>
       </c>
       <c r="G46" s="281" t="inlineStr">
         <is>
-          <t>Varilla Cobrizada para Puesta a Tierra, con Longitud de 2400 mm, diámetro de 14.28 mm y recubrimiento de 250 micras</t>
+          <t>Varilla maciza de cobre para puesta a tierra, diámetro 14.28 mm, longitud 2.40 m, conforme a referencia CC-E (12.7 a 25.4 mm x 2.40 m a 3.05 m)</t>
         </is>
       </c>
       <c r="H46" s="281" t="inlineStr">
         <is>
-          <t>Reglamento Técnico de Instalaciones Eléctricas RETIE Resolución 90708 de 2013 articulo 20 numerales 15.3.1 (Electrodos de Puesta a Tierra), 20.21 (Electrodos de Puesta a Tierra), 20.21.1 (Requisitos de producto) y NTC 2206:2001, numerales 10, 10.1, 10.2, 10.2.4 y 10.2.5</t>
+          <t>NTC 2206/2001 y Resolución 90708 de 2013 (RETIE, numeral 15.3)</t>
         </is>
       </c>
       <c r="I46" s="281" t="inlineStr">
         <is>
-          <t>PROELECTRA DE COLOMBIA S.A.S</t>
+          <t>COBRES DE COLOMBIA S.A.S.</t>
         </is>
       </c>
       <c r="J46" s="281" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="M46" s="281" t="inlineStr">
         <is>
-          <t>Componente esencial del sistema de puesta a tierra, permite la desviación de fallas de corriente o descargas atmosféricas a tierra</t>
+          <t>Componente principal del sistema de puesta a tierra, permite la interconexión de las varillas de puesta a tierra, formando un enmallado</t>
         </is>
       </c>
       <c r="N46" s="281" t="inlineStr">
@@ -5626,7 +5626,7 @@
     </row>
     <row r="47" ht="90.75" customHeight="1" s="169">
       <c r="A47" s="281" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B47" s="281" t="inlineStr">
         <is>
@@ -5635,31 +5635,31 @@
       </c>
       <c r="C47" s="281" t="n"/>
       <c r="D47" s="281" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E47" s="281" t="inlineStr">
         <is>
-          <t>Unidades</t>
+          <t>unidades</t>
         </is>
       </c>
       <c r="F47" s="281" t="inlineStr">
         <is>
-          <t>COBRES DE COLOMBIA S.A.S.</t>
+          <t>TECNOWELD</t>
         </is>
       </c>
       <c r="G47" s="281" t="inlineStr">
         <is>
-          <t>Varilla maciza de cobre para puesta a tierra, diámetro 14.28 mm, longitud 2.40 m, conforme a referencia CC-E (12.7 a 25.4 mm x 2.40 m a 3.05 m)</t>
+          <t>SG1TN 6519</t>
         </is>
       </c>
       <c r="H47" s="281" t="inlineStr">
         <is>
-          <t>NTC 2206/2001 y Resolución 90708 de 2013 (RETIE, numeral 15.3)</t>
+          <t>UL E359848</t>
         </is>
       </c>
       <c r="I47" s="281" t="inlineStr">
         <is>
-          <t>COBRES DE COLOMBIA S.A.S.</t>
+          <t>TECNOWELD</t>
         </is>
       </c>
       <c r="J47" s="281" t="inlineStr">
@@ -5668,25 +5668,25 @@
         </is>
       </c>
       <c r="K47" s="281" t="n">
-        <v>544529.0891999999</v>
+        <v>76211.00073489113</v>
       </c>
       <c r="L47" s="281" t="n">
-        <v>103460.526948</v>
+        <v>14480.09013962932</v>
       </c>
       <c r="M47" s="281" t="inlineStr">
         <is>
-          <t>Componente principal del sistema de puesta a tierra, permite la interconexión de las varillas de puesta a tierra, formando un enmallado</t>
+          <t>Elemento necesario para unir las derivaciones del sistema de puesta a tierra y para crear el enmallado</t>
         </is>
       </c>
       <c r="N47" s="281" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/17k0D3Iq77oQe-UuiCTdFj3qmrrBOhjpT</t>
+          <t>https://drive.google.com/drive/folders/1952XiGV0w36dsIiIExLhkqevtMrpHBRI</t>
         </is>
       </c>
       <c r="O47" s="281" t="n"/>
       <c r="P47" s="281" t="inlineStr">
         <is>
-          <t>P01118</t>
+          <t>P00723</t>
         </is>
       </c>
       <c r="Q47" s="281" t="n"/>
@@ -5704,7 +5704,7 @@
     </row>
     <row r="48" ht="90.75" customHeight="1" s="169">
       <c r="A48" s="281" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B48" s="281" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G48" s="281" t="inlineStr">
         <is>
-          <t>SG1TN 6519</t>
+          <t>SG1TN 2694</t>
         </is>
       </c>
       <c r="H48" s="281" t="inlineStr">
@@ -5764,7 +5764,7 @@
       <c r="O48" s="281" t="n"/>
       <c r="P48" s="281" t="inlineStr">
         <is>
-          <t>P00723</t>
+          <t>P01244</t>
         </is>
       </c>
       <c r="Q48" s="281" t="n"/>
@@ -5782,7 +5782,7 @@
     </row>
     <row r="49" ht="90.75" customHeight="1" s="169">
       <c r="A49" s="281" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B49" s="281" t="inlineStr">
         <is>
@@ -5805,7 +5805,7 @@
       </c>
       <c r="G49" s="281" t="inlineStr">
         <is>
-          <t>SG1TN 2694</t>
+          <t>SG1TN 228*</t>
         </is>
       </c>
       <c r="H49" s="281" t="inlineStr">
@@ -5842,7 +5842,7 @@
       <c r="O49" s="281" t="n"/>
       <c r="P49" s="281" t="inlineStr">
         <is>
-          <t>P01244</t>
+          <t>P00728</t>
         </is>
       </c>
       <c r="Q49" s="281" t="n"/>
@@ -5860,16 +5860,16 @@
     </row>
     <row r="50" ht="90.75" customHeight="1" s="169">
       <c r="A50" s="281" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B50" s="281" t="inlineStr">
         <is>
-          <t>Elementos o equipos para el sistema de puesta a tierra (varillas, mallas, grapas, conectores)</t>
+          <t>Fusibles y porta fusibles</t>
         </is>
       </c>
       <c r="C50" s="281" t="n"/>
       <c r="D50" s="281" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E50" s="281" t="inlineStr">
         <is>
@@ -5878,49 +5878,49 @@
       </c>
       <c r="F50" s="281" t="inlineStr">
         <is>
-          <t>TECNOWELD</t>
+          <t>CELSA</t>
         </is>
       </c>
       <c r="G50" s="281" t="inlineStr">
         <is>
-          <t>SG1TN 228*</t>
+          <t>CORTACIRCUITOS 27 KV 100A 12 kA IX2712512</t>
         </is>
       </c>
       <c r="H50" s="281" t="inlineStr">
         <is>
-          <t>UL E359848</t>
+          <t>ANSI C37.41 (NTC2132) y ANSI C37.42 (NTC 2133.)</t>
         </is>
       </c>
       <c r="I50" s="281" t="inlineStr">
         <is>
-          <t>TECNOWELD</t>
+          <t>CELSA S.A.S.</t>
         </is>
       </c>
       <c r="J50" s="281" t="inlineStr">
         <is>
-          <t>EDEMCO</t>
+          <t>EDEMCO S.A.S.</t>
         </is>
       </c>
       <c r="K50" s="281" t="n">
-        <v>0</v>
+        <v>1860000</v>
       </c>
       <c r="L50" s="281" t="n">
-        <v>0</v>
+        <v>353400</v>
       </c>
       <c r="M50" s="281" t="inlineStr">
         <is>
-          <t>Elemento necesario para unir las derivaciones del sistema de puesta a tierra y para crear el enmallado</t>
+          <t>Corta el paso de corriente cuando se detecta una sobrecarga en el circuito</t>
         </is>
       </c>
       <c r="N50" s="281" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1952XiGV0w36dsIiIExLhkqevtMrpHBRI</t>
+          <t>https://drive.google.com/drive/folders/1OPYaLQLL6VZHhXpN15KvOt-I2PiB0Fu0</t>
         </is>
       </c>
       <c r="O50" s="281" t="n"/>
       <c r="P50" s="281" t="inlineStr">
         <is>
-          <t>P00728</t>
+          <t>P00503</t>
         </is>
       </c>
       <c r="Q50" s="281" t="n"/>
@@ -5938,7 +5938,7 @@
     </row>
     <row r="51" ht="90.75" customHeight="1" s="169">
       <c r="A51" s="281" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B51" s="281" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="C51" s="281" t="n"/>
       <c r="D51" s="281" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E51" s="281" t="inlineStr">
         <is>
@@ -5956,49 +5956,51 @@
       </c>
       <c r="F51" s="281" t="inlineStr">
         <is>
-          <t>CELSA</t>
+          <t>LUHFSER</t>
         </is>
       </c>
       <c r="G51" s="281" t="inlineStr">
         <is>
-          <t>CORTACIRCUITOS 27 KV 100A 12 kA IX2712512</t>
+          <t>Tipo K de 1 Amperio para 15 kV - Frecuencia 50-60 Hz</t>
         </is>
       </c>
       <c r="H51" s="281" t="inlineStr">
         <is>
-          <t>ANSI C37.41 (NTC2132) y ANSI C37.42 (NTC 2133.)</t>
+          <t>Numeral 20.19 del Reglamento Técnico de Instalaciones Eléctricas - RETIE. Resolución 90708 de 30 de agosto de 2013 del Ministerio de Minas y Energías.
+IEEE Std C37.41-2016/Cor 1-2017, IEEE Std C37,42-2016,
+NTC 2132-2006, NTC 2133 2002.</t>
         </is>
       </c>
       <c r="I51" s="281" t="inlineStr">
         <is>
-          <t>CELSA S.A.S.</t>
+          <t>ELÉCTRICOS INTERNACIONAL SAS.</t>
         </is>
       </c>
       <c r="J51" s="281" t="inlineStr">
         <is>
-          <t>EDEMCO S.A.S.</t>
+          <t>IE INTER ELECTRICAS</t>
         </is>
       </c>
       <c r="K51" s="281" t="n">
-        <v>1860000</v>
+        <v>120000</v>
       </c>
       <c r="L51" s="281" t="n">
-        <v>353400</v>
+        <v>22800</v>
       </c>
       <c r="M51" s="281" t="inlineStr">
         <is>
-          <t>Corta el paso de corriente cuando se detecta una sobrecarga en el circuito</t>
+          <t>Corta el paso de corriente cuando se detecta una sobrecarga en el circuito para proteger el transformador y los circuitos ramales</t>
         </is>
       </c>
       <c r="N51" s="281" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1OPYaLQLL6VZHhXpN15KvOt-I2PiB0Fu0</t>
+          <t>https://drive.google.com/drive/folders/1Avw32_rbo6CYnhy6rrgWk4I6QwIKCB1N</t>
         </is>
       </c>
       <c r="O51" s="281" t="n"/>
       <c r="P51" s="281" t="inlineStr">
         <is>
-          <t>P00503</t>
+          <t>P00588</t>
         </is>
       </c>
       <c r="Q51" s="281" t="n"/>
@@ -6016,69 +6018,67 @@
     </row>
     <row r="52" ht="90.75" customHeight="1" s="169">
       <c r="A52" s="281" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B52" s="281" t="inlineStr">
         <is>
-          <t>Fusibles y porta fusibles</t>
+          <t xml:space="preserve">Tableros de baja tensión AC/DC (Incluye los elementos internos) </t>
         </is>
       </c>
       <c r="C52" s="281" t="n"/>
       <c r="D52" s="281" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E52" s="281" t="inlineStr">
         <is>
-          <t>unidades</t>
+          <t>unidad</t>
         </is>
       </c>
       <c r="F52" s="281" t="inlineStr">
         <is>
-          <t>LUHFSER</t>
+          <t>TODO LÁMINAS C.E.</t>
         </is>
       </c>
       <c r="G52" s="281" t="inlineStr">
         <is>
-          <t>Tipo K de 1 Amperio para 15 kV - Frecuencia 50-60 Hz</t>
+          <t>TMI (2) - 100 A- 10 kA - IP 44 - 600,700,250 - enero 2026</t>
         </is>
       </c>
       <c r="H52" s="281" t="inlineStr">
         <is>
-          <t>Numeral 20.19 del Reglamento Técnico de Instalaciones Eléctricas - RETIE. Resolución 90708 de 30 de agosto de 2013 del Ministerio de Minas y Energías.
-IEEE Std C37.41-2016/Cor 1-2017, IEEE Std C37,42-2016,
-NTC 2132-2006, NTC 2133 2002.</t>
+          <t>Numeral 20.23-1 del Reglamento Técnico de Instalaciones Eléctricas - RETIE. Resolución 90708 del 30 de agosto de 2013 y 90795 del 25 de julio de 2014 del Ministerio de Minas y Energía</t>
         </is>
       </c>
       <c r="I52" s="281" t="inlineStr">
         <is>
-          <t>ELÉCTRICOS INTERNACIONAL SAS.</t>
+          <t>TODO LÁMINAS C.E.</t>
         </is>
       </c>
       <c r="J52" s="281" t="inlineStr">
         <is>
-          <t>IE INTER ELECTRICAS</t>
+          <t>MAVILL</t>
         </is>
       </c>
       <c r="K52" s="281" t="n">
-        <v>120000</v>
+        <v>3060000</v>
       </c>
       <c r="L52" s="281" t="n">
-        <v>22800</v>
+        <v>581400</v>
       </c>
       <c r="M52" s="281" t="inlineStr">
         <is>
-          <t>Corta el paso de corriente cuando se detecta una sobrecarga en el circuito para proteger el transformador y los circuitos ramales</t>
+          <t>Alberga los dos medidores de energía de la frontera del proyecto</t>
         </is>
       </c>
       <c r="N52" s="281" t="inlineStr">
         <is>
-          <t>https://drive.google.com/drive/folders/1Avw32_rbo6CYnhy6rrgWk4I6QwIKCB1N</t>
+          <t>https://drive.google.com/file/d/1gLijv4GyNTq7jeEBLdmXbZnNpyotSbFJ/view?usp=drive_link</t>
         </is>
       </c>
       <c r="O52" s="281" t="n"/>
       <c r="P52" s="281" t="inlineStr">
         <is>
-          <t>P00588</t>
+          <t>P00609</t>
         </is>
       </c>
       <c r="Q52" s="281" t="n"/>
@@ -6096,67 +6096,67 @@
     </row>
     <row r="53" ht="90.75" customHeight="1" s="169">
       <c r="A53" s="281" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B53" s="281" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tableros de baja tensión AC/DC (Incluye los elementos internos) </t>
+          <t>Canalizaciones: canaletas, tubos, prefabricadas con barras o con cables, ductos subterráneos</t>
         </is>
       </c>
       <c r="C53" s="281" t="n"/>
       <c r="D53" s="281" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E53" s="281" t="inlineStr">
         <is>
-          <t>unidad</t>
+          <t>unidades</t>
         </is>
       </c>
       <c r="F53" s="281" t="inlineStr">
         <is>
-          <t>TODO LÁMINAS C.E.</t>
+          <t>ColmenaConduit</t>
         </is>
       </c>
       <c r="G53" s="281" t="inlineStr">
         <is>
-          <t>TMI (2) - 100 A- 10 kA - IP 44 - 600,700,250 - enero 2026</t>
+          <t>IMC Diámetro 4"</t>
         </is>
       </c>
       <c r="H53" s="281" t="inlineStr">
         <is>
-          <t>Numeral 20.23-1 del Reglamento Técnico de Instalaciones Eléctricas - RETIE. Resolución 90708 del 30 de agosto de 2013 y 90795 del 25 de julio de 2014 del Ministerio de Minas y Energía</t>
+          <t>RESOLUCIÓN 90708 de 2013 del MINISTERIO DE MINAS Y ENERGÍA – RETIE (Numeral 20.6)</t>
         </is>
       </c>
       <c r="I53" s="281" t="inlineStr">
         <is>
-          <t>TODO LÁMINAS C.E.</t>
+          <t>CONSORCIO METALÚRGICO NACIONAL S.A.S – COLMENA S.A.S.</t>
         </is>
       </c>
       <c r="J53" s="281" t="inlineStr">
         <is>
-          <t>MAVILL</t>
+          <t>IE INTERELECTRICAS</t>
         </is>
       </c>
       <c r="K53" s="281" t="n">
-        <v>3060000</v>
+        <v>366872.0821661998</v>
       </c>
       <c r="L53" s="281" t="n">
-        <v>581400</v>
+        <v>69705.69561157796</v>
       </c>
       <c r="M53" s="281" t="inlineStr">
         <is>
-          <t>Alberga los dos medidores de energía de la frontera del proyecto</t>
+          <t>La tubería se encarga de proteger el cableado AC en media tensión que es instalado desde la celda de protección hasta el punto de interconexión a la red del Operador de Red</t>
         </is>
       </c>
       <c r="N53" s="281" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1gLijv4GyNTq7jeEBLdmXbZnNpyotSbFJ/view?usp=drive_link</t>
+          <t>https://drive.google.com/drive/folders/1MhO1h59Q9qXK_vTaK-CIkpbl3K6HpvYJ</t>
         </is>
       </c>
       <c r="O53" s="281" t="n"/>
       <c r="P53" s="281" t="inlineStr">
         <is>
-          <t>P00609</t>
+          <t>P00049</t>
         </is>
       </c>
       <c r="Q53" s="281" t="n"/>
@@ -6174,7 +6174,7 @@
     </row>
     <row r="54" ht="90.75" customHeight="1" s="169">
       <c r="A54" s="281" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B54" s="281" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
       </c>
       <c r="C54" s="281" t="n"/>
       <c r="D54" s="281" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="E54" s="281" t="inlineStr">
         <is>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="G54" s="281" t="inlineStr">
         <is>
-          <t>IMC Diámetro 4"</t>
+          <t>IMC Diámetro 3/4"</t>
         </is>
       </c>
       <c r="H54" s="281" t="inlineStr">
@@ -6216,10 +6216,10 @@
         </is>
       </c>
       <c r="K54" s="281" t="n">
-        <v>366872.0821661998</v>
+        <v>797142.857142857</v>
       </c>
       <c r="L54" s="281" t="n">
-        <v>69705.69561157796</v>
+        <v>151457.1428571428</v>
       </c>
       <c r="M54" s="281" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
       <c r="O54" s="281" t="n"/>
       <c r="P54" s="281" t="inlineStr">
         <is>
-          <t>P00049</t>
+          <t>P00046</t>
         </is>
       </c>
       <c r="Q54" s="281" t="n"/>
@@ -6250,84 +6250,7 @@
       <c r="AA54" s="281" t="n"/>
       <c r="AB54" s="281" t="n"/>
     </row>
-    <row r="55" ht="90.75" customHeight="1" s="169">
-      <c r="A55" s="281" t="n">
-        <v>101</v>
-      </c>
-      <c r="B55" s="281" t="inlineStr">
-        <is>
-          <t>Canalizaciones: canaletas, tubos, prefabricadas con barras o con cables, ductos subterráneos</t>
-        </is>
-      </c>
-      <c r="C55" s="281" t="n"/>
-      <c r="D55" s="281" t="n">
-        <v>18</v>
-      </c>
-      <c r="E55" s="281" t="inlineStr">
-        <is>
-          <t>unidades</t>
-        </is>
-      </c>
-      <c r="F55" s="281" t="inlineStr">
-        <is>
-          <t>ColmenaConduit</t>
-        </is>
-      </c>
-      <c r="G55" s="281" t="inlineStr">
-        <is>
-          <t>IMC Diámetro 3/4"</t>
-        </is>
-      </c>
-      <c r="H55" s="281" t="inlineStr">
-        <is>
-          <t>RESOLUCIÓN 90708 de 2013 del MINISTERIO DE MINAS Y ENERGÍA – RETIE (Numeral 20.6)</t>
-        </is>
-      </c>
-      <c r="I55" s="281" t="inlineStr">
-        <is>
-          <t>CONSORCIO METALÚRGICO NACIONAL S.A.S – COLMENA S.A.S.</t>
-        </is>
-      </c>
-      <c r="J55" s="281" t="inlineStr">
-        <is>
-          <t>IE INTERELECTRICAS</t>
-        </is>
-      </c>
-      <c r="K55" s="281" t="n">
-        <v>797142.857142857</v>
-      </c>
-      <c r="L55" s="281" t="n">
-        <v>151457.1428571428</v>
-      </c>
-      <c r="M55" s="281" t="inlineStr">
-        <is>
-          <t>La tubería se encarga de proteger el cableado AC en media tensión que es instalado desde la celda de protección hasta el punto de interconexión a la red del Operador de Red</t>
-        </is>
-      </c>
-      <c r="N55" s="281" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/drive/folders/1MhO1h59Q9qXK_vTaK-CIkpbl3K6HpvYJ</t>
-        </is>
-      </c>
-      <c r="O55" s="281" t="n"/>
-      <c r="P55" s="281" t="inlineStr">
-        <is>
-          <t>P00046</t>
-        </is>
-      </c>
-      <c r="Q55" s="281" t="n"/>
-      <c r="R55" s="281" t="n"/>
-      <c r="S55" s="281" t="n"/>
-      <c r="T55" s="281" t="n"/>
-      <c r="U55" s="281" t="n"/>
-      <c r="V55" s="281" t="n"/>
-      <c r="W55" s="281" t="n"/>
-      <c r="X55" s="281" t="n"/>
-      <c r="Y55" s="281" t="n"/>
-      <c r="Z55" s="281" t="n"/>
-      <c r="AA55" s="281" t="n"/>
-      <c r="AB55" s="281" t="n"/>
-    </row>
+    <row r="55" ht="90.75" customHeight="1" s="169"/>
     <row r="56" ht="90.75" customHeight="1" s="169"/>
     <row r="57" ht="90.75" customHeight="1" s="169"/>
     <row r="58" ht="90.75" customHeight="1" s="169" thickBot="1"/>
@@ -6368,24 +6291,24 @@
     <row r="93" ht="90.75" customHeight="1" s="169"/>
     <row r="94" ht="90.75" customHeight="1" s="169"/>
     <row r="95" ht="90.75" customHeight="1" s="169"/>
-    <row r="96" ht="90.75" customHeight="1" s="169"/>
-    <row r="97" ht="106.5" customHeight="1" s="169"/>
+    <row r="96" ht="106.5" customHeight="1" s="169"/>
+    <row r="97" ht="90.75" customHeight="1" s="169" thickBot="1"/>
     <row r="98" ht="90.75" customHeight="1" s="169" thickBot="1"/>
     <row r="99" ht="90.75" customHeight="1" s="169" thickBot="1"/>
-    <row r="100" ht="90.75" customHeight="1" s="169" thickBot="1"/>
+    <row r="100" ht="90.75" customHeight="1" s="169"/>
     <row r="101" ht="90.75" customHeight="1" s="169"/>
     <row r="102" ht="90.75" customHeight="1" s="169"/>
     <row r="103" ht="90.75" customHeight="1" s="169"/>
-    <row r="104" ht="90.75" customHeight="1" s="169"/>
-    <row r="105" ht="108.75" customHeight="1" s="169"/>
+    <row r="104" ht="108.75" customHeight="1" s="169"/>
+    <row r="105" ht="90.75" customHeight="1" s="169"/>
     <row r="106" ht="90.75" customHeight="1" s="169"/>
-    <row r="107" ht="90.75" customHeight="1" s="169"/>
+    <row r="107" ht="14.25" customHeight="1" s="169"/>
     <row r="108" ht="14.25" customHeight="1" s="169"/>
-    <row r="109" ht="14.25" customHeight="1" s="169"/>
+    <row r="109" ht="14.25" customHeight="1" s="169" thickBot="1"/>
     <row r="110" ht="14.25" customHeight="1" s="169" thickBot="1"/>
     <row r="111" ht="14.25" customHeight="1" s="169" thickBot="1"/>
     <row r="112" ht="14.25" customHeight="1" s="169" thickBot="1"/>
-    <row r="113" ht="14.25" customHeight="1" s="169" thickBot="1"/>
+    <row r="113" ht="14.25" customHeight="1" s="169"/>
     <row r="114" ht="14.25" customHeight="1" s="169"/>
     <row r="115" ht="14.25" customHeight="1" s="169"/>
     <row r="116" ht="14.25" customHeight="1" s="169"/>
@@ -6484,8 +6407,8 @@
     <row r="209" ht="14.25" customHeight="1" s="169"/>
     <row r="210" ht="14.25" customHeight="1" s="169"/>
     <row r="211" ht="14.25" customHeight="1" s="169"/>
-    <row r="212" ht="14.25" customHeight="1" s="169"/>
-    <row r="213" ht="13.5" customHeight="1" s="169"/>
+    <row r="212" ht="13.5" customHeight="1" s="169"/>
+    <row r="213" ht="14.25" customHeight="1" s="169"/>
     <row r="214" ht="14.25" customHeight="1" s="169"/>
     <row r="215" ht="14.25" customHeight="1" s="169"/>
     <row r="216" ht="14.25" customHeight="1" s="169"/>
@@ -6684,7 +6607,7 @@
     <row r="409" ht="14.25" customHeight="1" s="169"/>
     <row r="410" ht="14.25" customHeight="1" s="169"/>
     <row r="411" ht="14.25" customHeight="1" s="169"/>
-    <row r="412" ht="14.25" customHeight="1" s="169"/>
+    <row r="412" ht="15.75" customHeight="1" s="169"/>
     <row r="413" ht="15.75" customHeight="1" s="169"/>
     <row r="414" ht="15.75" customHeight="1" s="169"/>
     <row r="415" ht="15.75" customHeight="1" s="169"/>
@@ -7408,7 +7331,6 @@
     <row r="1133" ht="15.75" customHeight="1" s="169"/>
     <row r="1134" ht="15.75" customHeight="1" s="169"/>
     <row r="1135" ht="15.75" customHeight="1" s="169"/>
-    <row r="1136" ht="15.75" customHeight="1" s="169"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:B5"/>
@@ -7427,22 +7349,22 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K99:K100">
+  <conditionalFormatting sqref="K98:K99">
     <cfRule type="cellIs" priority="2" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K111:K113">
+  <conditionalFormatting sqref="K110:K112">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation sqref="K12:K19 K21:K35 K59 K108:L109 K114:L212 L110" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal">
+    <dataValidation sqref="K12:K19 K21:K35 K59 K107:L108 K113:L211 L109" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="decimal">
       <formula1>0</formula1>
       <formula2>1E+21</formula2>
     </dataValidation>
-    <dataValidation sqref="K110 L31:L35 M13:M17 M108:M109 M114:M212" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="custom">
+    <dataValidation sqref="K109 L31:L35 M13:M17 M107:M108 M113:M211" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="custom">
       <formula1>LT(LEN(K13),(450))</formula1>
     </dataValidation>
     <dataValidation sqref="M68:M69" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="textLength" operator="lessThan">
